--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7FA206-7A41-4CF9-87FA-A96BC6CA3041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A941C9ED-7D6C-429D-BCC2-82FF06B524F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="1440" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -6392,6 +6392,464 @@
         <v>11.4</v>
       </c>
     </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B366" t="b">
+        <v>0</v>
+      </c>
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366">
+        <v>15.2</v>
+      </c>
+      <c r="E366">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B367" t="b">
+        <v>0</v>
+      </c>
+      <c r="C367" t="s">
+        <v>6</v>
+      </c>
+      <c r="D367">
+        <v>12.8</v>
+      </c>
+      <c r="E367">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B368" t="b">
+        <v>0</v>
+      </c>
+      <c r="C368" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368">
+        <v>14.2</v>
+      </c>
+      <c r="E368">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B369" t="b">
+        <v>0</v>
+      </c>
+      <c r="C369" t="s">
+        <v>8</v>
+      </c>
+      <c r="D369">
+        <v>13.9</v>
+      </c>
+      <c r="E369">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B370" t="b">
+        <v>0</v>
+      </c>
+      <c r="C370" t="s">
+        <v>9</v>
+      </c>
+      <c r="D370">
+        <v>11.7</v>
+      </c>
+      <c r="E370">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B371" t="b">
+        <v>0</v>
+      </c>
+      <c r="C371" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B372" t="b">
+        <v>0</v>
+      </c>
+      <c r="C372" t="s">
+        <v>11</v>
+      </c>
+      <c r="D372">
+        <v>14.3</v>
+      </c>
+      <c r="E372">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B373" t="b">
+        <v>0</v>
+      </c>
+      <c r="C373" t="s">
+        <v>12</v>
+      </c>
+      <c r="D373">
+        <v>10.3</v>
+      </c>
+      <c r="E373">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B374" t="b">
+        <v>0</v>
+      </c>
+      <c r="C374" t="s">
+        <v>13</v>
+      </c>
+      <c r="D374">
+        <v>15.1</v>
+      </c>
+      <c r="E374">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B375" t="b">
+        <v>0</v>
+      </c>
+      <c r="C375" t="s">
+        <v>14</v>
+      </c>
+      <c r="D375">
+        <v>12.7</v>
+      </c>
+      <c r="E375">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B376" t="b">
+        <v>0</v>
+      </c>
+      <c r="C376" t="s">
+        <v>15</v>
+      </c>
+      <c r="D376">
+        <v>12.8</v>
+      </c>
+      <c r="E376">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B377" t="b">
+        <v>0</v>
+      </c>
+      <c r="C377" t="s">
+        <v>16</v>
+      </c>
+      <c r="D377">
+        <v>13.5</v>
+      </c>
+      <c r="E377">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B378" t="b">
+        <v>0</v>
+      </c>
+      <c r="C378" t="s">
+        <v>17</v>
+      </c>
+      <c r="D378">
+        <v>13.2</v>
+      </c>
+      <c r="E378">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B379" t="b">
+        <v>0</v>
+      </c>
+      <c r="C379" t="s">
+        <v>18</v>
+      </c>
+      <c r="D379">
+        <v>13.5</v>
+      </c>
+      <c r="E379">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B380" t="b">
+        <v>0</v>
+      </c>
+      <c r="C380" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B381" t="b">
+        <v>0</v>
+      </c>
+      <c r="C381" t="s">
+        <v>20</v>
+      </c>
+      <c r="D381">
+        <v>13.3</v>
+      </c>
+      <c r="E381">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B382" t="b">
+        <v>0</v>
+      </c>
+      <c r="C382" t="s">
+        <v>21</v>
+      </c>
+      <c r="D382">
+        <v>15.2</v>
+      </c>
+      <c r="E382">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B383" t="b">
+        <v>0</v>
+      </c>
+      <c r="C383" t="s">
+        <v>22</v>
+      </c>
+      <c r="D383">
+        <v>11.3</v>
+      </c>
+      <c r="E383">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B384" t="b">
+        <v>0</v>
+      </c>
+      <c r="C384" t="s">
+        <v>23</v>
+      </c>
+      <c r="D384">
+        <v>15.2</v>
+      </c>
+      <c r="E384">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B385" t="b">
+        <v>0</v>
+      </c>
+      <c r="C385" t="s">
+        <v>24</v>
+      </c>
+      <c r="D385">
+        <v>13.2</v>
+      </c>
+      <c r="E385">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B386" t="b">
+        <v>0</v>
+      </c>
+      <c r="C386" t="s">
+        <v>25</v>
+      </c>
+      <c r="D386">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E386">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B387" t="b">
+        <v>0</v>
+      </c>
+      <c r="C387" t="s">
+        <v>26</v>
+      </c>
+      <c r="D387">
+        <v>13.3</v>
+      </c>
+      <c r="E387">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B388" t="b">
+        <v>0</v>
+      </c>
+      <c r="C388" t="s">
+        <v>27</v>
+      </c>
+      <c r="D388">
+        <v>16</v>
+      </c>
+      <c r="E388">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B389" t="b">
+        <v>0</v>
+      </c>
+      <c r="C389" t="s">
+        <v>28</v>
+      </c>
+      <c r="D389">
+        <v>16</v>
+      </c>
+      <c r="E389">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B390" t="b">
+        <v>0</v>
+      </c>
+      <c r="C390" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B391" t="b">
+        <v>0</v>
+      </c>
+      <c r="C391" t="s">
+        <v>30</v>
+      </c>
+      <c r="D391">
+        <v>13.2</v>
+      </c>
+      <c r="E391">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B392" t="b">
+        <v>0</v>
+      </c>
+      <c r="C392" t="s">
+        <v>31</v>
+      </c>
+      <c r="D392">
+        <v>12.2</v>
+      </c>
+      <c r="E392">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B393" t="b">
+        <v>0</v>
+      </c>
+      <c r="C393" t="s">
+        <v>32</v>
+      </c>
+      <c r="D393">
+        <v>12.1</v>
+      </c>
+      <c r="E393">
+        <v>11.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A941C9ED-7D6C-429D-BCC2-82FF06B524F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114C644D-7690-4857-B9CF-E9FECAC30E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E421"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -6850,6 +6850,452 @@
         <v>11.4</v>
       </c>
     </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B394" t="b">
+        <v>0</v>
+      </c>
+      <c r="C394" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394">
+        <v>15.7</v>
+      </c>
+      <c r="E394">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B395" t="b">
+        <v>0</v>
+      </c>
+      <c r="C395" t="s">
+        <v>6</v>
+      </c>
+      <c r="D395">
+        <v>13.6</v>
+      </c>
+      <c r="E395">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B396" t="b">
+        <v>0</v>
+      </c>
+      <c r="C396" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396">
+        <v>14.2</v>
+      </c>
+      <c r="E396">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B397" t="b">
+        <v>0</v>
+      </c>
+      <c r="C397" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B398" t="b">
+        <v>0</v>
+      </c>
+      <c r="C398" t="s">
+        <v>9</v>
+      </c>
+      <c r="D398">
+        <v>12.4</v>
+      </c>
+      <c r="E398">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B399" t="b">
+        <v>0</v>
+      </c>
+      <c r="C399" t="s">
+        <v>10</v>
+      </c>
+      <c r="D399">
+        <v>12.4</v>
+      </c>
+      <c r="E399">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B400" t="b">
+        <v>0</v>
+      </c>
+      <c r="C400" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A401" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B401" t="b">
+        <v>0</v>
+      </c>
+      <c r="C401" t="s">
+        <v>12</v>
+      </c>
+      <c r="D401">
+        <v>10.9</v>
+      </c>
+      <c r="E401">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A402" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B402" t="b">
+        <v>0</v>
+      </c>
+      <c r="C402" t="s">
+        <v>13</v>
+      </c>
+      <c r="D402">
+        <v>14</v>
+      </c>
+      <c r="E402">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A403" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B403" t="b">
+        <v>0</v>
+      </c>
+      <c r="C403" t="s">
+        <v>14</v>
+      </c>
+      <c r="D403">
+        <v>13.5</v>
+      </c>
+      <c r="E403">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A404" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B404" t="b">
+        <v>0</v>
+      </c>
+      <c r="C404" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A405" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B405" t="b">
+        <v>0</v>
+      </c>
+      <c r="C405" t="s">
+        <v>16</v>
+      </c>
+      <c r="D405">
+        <v>14.1</v>
+      </c>
+      <c r="E405">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A406" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B406" t="b">
+        <v>0</v>
+      </c>
+      <c r="C406" t="s">
+        <v>17</v>
+      </c>
+      <c r="D406">
+        <v>12.7</v>
+      </c>
+      <c r="E406">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A407" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B407" t="b">
+        <v>0</v>
+      </c>
+      <c r="C407" t="s">
+        <v>18</v>
+      </c>
+      <c r="D407">
+        <v>13.4</v>
+      </c>
+      <c r="E407">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A408" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B408" t="b">
+        <v>0</v>
+      </c>
+      <c r="C408" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A409" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B409" t="b">
+        <v>0</v>
+      </c>
+      <c r="C409" t="s">
+        <v>20</v>
+      </c>
+      <c r="D409">
+        <v>12.4</v>
+      </c>
+      <c r="E409">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A410" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B410" t="b">
+        <v>0</v>
+      </c>
+      <c r="C410" t="s">
+        <v>21</v>
+      </c>
+      <c r="D410">
+        <v>14.8</v>
+      </c>
+      <c r="E410">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A411" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B411" t="b">
+        <v>0</v>
+      </c>
+      <c r="C411" t="s">
+        <v>22</v>
+      </c>
+      <c r="D411">
+        <v>10.8</v>
+      </c>
+      <c r="E411">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A412" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B412" t="b">
+        <v>0</v>
+      </c>
+      <c r="C412" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A413" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B413" t="b">
+        <v>0</v>
+      </c>
+      <c r="C413" t="s">
+        <v>24</v>
+      </c>
+      <c r="D413">
+        <v>13.9</v>
+      </c>
+      <c r="E413">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A414" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B414" t="b">
+        <v>0</v>
+      </c>
+      <c r="C414" t="s">
+        <v>25</v>
+      </c>
+      <c r="D414">
+        <v>9</v>
+      </c>
+      <c r="E414">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A415" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B415" t="b">
+        <v>0</v>
+      </c>
+      <c r="C415" t="s">
+        <v>26</v>
+      </c>
+      <c r="D415">
+        <v>13</v>
+      </c>
+      <c r="E415">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A416" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B416" t="b">
+        <v>0</v>
+      </c>
+      <c r="C416" t="s">
+        <v>27</v>
+      </c>
+      <c r="D416">
+        <v>15</v>
+      </c>
+      <c r="E416">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A417" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B417" t="b">
+        <v>0</v>
+      </c>
+      <c r="C417" t="s">
+        <v>28</v>
+      </c>
+      <c r="D417">
+        <v>16.8</v>
+      </c>
+      <c r="E417">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A418" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B418" t="b">
+        <v>0</v>
+      </c>
+      <c r="C418" t="s">
+        <v>29</v>
+      </c>
+      <c r="D418">
+        <v>13.3</v>
+      </c>
+      <c r="E418">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A419" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B419" t="b">
+        <v>0</v>
+      </c>
+      <c r="C419" t="s">
+        <v>30</v>
+      </c>
+      <c r="D419">
+        <v>12.6</v>
+      </c>
+      <c r="E419">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A420" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B420" t="b">
+        <v>0</v>
+      </c>
+      <c r="C420" t="s">
+        <v>31</v>
+      </c>
+      <c r="D420">
+        <v>13</v>
+      </c>
+      <c r="E420">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A421" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B421" t="b">
+        <v>0</v>
+      </c>
+      <c r="C421" t="s">
+        <v>32</v>
+      </c>
+      <c r="D421">
+        <v>12.7</v>
+      </c>
+      <c r="E421">
+        <v>11.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114C644D-7690-4857-B9CF-E9FECAC30E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A1C21F-8505-41A4-BEA3-B39A3A03BEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E421"/>
+  <dimension ref="A1:E449"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -7296,6 +7296,470 @@
         <v>11.7</v>
       </c>
     </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B422" t="b">
+        <v>0</v>
+      </c>
+      <c r="C422" t="s">
+        <v>5</v>
+      </c>
+      <c r="D422">
+        <v>16.3</v>
+      </c>
+      <c r="E422">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B423" t="b">
+        <v>0</v>
+      </c>
+      <c r="C423" t="s">
+        <v>6</v>
+      </c>
+      <c r="D423">
+        <v>13.3</v>
+      </c>
+      <c r="E423">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B424" t="b">
+        <v>0</v>
+      </c>
+      <c r="C424" t="s">
+        <v>7</v>
+      </c>
+      <c r="D424">
+        <v>15.3</v>
+      </c>
+      <c r="E424">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B425" t="b">
+        <v>0</v>
+      </c>
+      <c r="C425" t="s">
+        <v>8</v>
+      </c>
+      <c r="D425">
+        <v>13.8</v>
+      </c>
+      <c r="E425">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B426" t="b">
+        <v>0</v>
+      </c>
+      <c r="C426" t="s">
+        <v>9</v>
+      </c>
+      <c r="D426">
+        <v>12.8</v>
+      </c>
+      <c r="E426">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B427" t="b">
+        <v>0</v>
+      </c>
+      <c r="C427" t="s">
+        <v>10</v>
+      </c>
+      <c r="D427">
+        <v>12.6</v>
+      </c>
+      <c r="E427">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B428" t="b">
+        <v>0</v>
+      </c>
+      <c r="C428" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428">
+        <v>15.3</v>
+      </c>
+      <c r="E428">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B429" t="b">
+        <v>0</v>
+      </c>
+      <c r="C429" t="s">
+        <v>12</v>
+      </c>
+      <c r="D429">
+        <v>10.8</v>
+      </c>
+      <c r="E429">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B430" t="b">
+        <v>0</v>
+      </c>
+      <c r="C430" t="s">
+        <v>13</v>
+      </c>
+      <c r="D430">
+        <v>13.9</v>
+      </c>
+      <c r="E430">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B431" t="b">
+        <v>0</v>
+      </c>
+      <c r="C431" t="s">
+        <v>14</v>
+      </c>
+      <c r="D431">
+        <v>13.5</v>
+      </c>
+      <c r="E431">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B432" t="b">
+        <v>0</v>
+      </c>
+      <c r="C432" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B433" t="b">
+        <v>0</v>
+      </c>
+      <c r="C433" t="s">
+        <v>16</v>
+      </c>
+      <c r="D433">
+        <v>14.3</v>
+      </c>
+      <c r="E433">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B434" t="b">
+        <v>0</v>
+      </c>
+      <c r="C434" t="s">
+        <v>17</v>
+      </c>
+      <c r="D434">
+        <v>12.7</v>
+      </c>
+      <c r="E434">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B435" t="b">
+        <v>0</v>
+      </c>
+      <c r="C435" t="s">
+        <v>18</v>
+      </c>
+      <c r="D435">
+        <v>14.1</v>
+      </c>
+      <c r="E435">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B436" t="b">
+        <v>0</v>
+      </c>
+      <c r="C436" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B437" t="b">
+        <v>0</v>
+      </c>
+      <c r="C437" t="s">
+        <v>20</v>
+      </c>
+      <c r="D437">
+        <v>12.5</v>
+      </c>
+      <c r="E437">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A438" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B438" t="b">
+        <v>0</v>
+      </c>
+      <c r="C438" t="s">
+        <v>21</v>
+      </c>
+      <c r="D438">
+        <v>15.2</v>
+      </c>
+      <c r="E438">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A439" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B439" t="b">
+        <v>0</v>
+      </c>
+      <c r="C439" t="s">
+        <v>22</v>
+      </c>
+      <c r="D439">
+        <v>10.9</v>
+      </c>
+      <c r="E439">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A440" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B440" t="b">
+        <v>0</v>
+      </c>
+      <c r="C440" t="s">
+        <v>23</v>
+      </c>
+      <c r="D440">
+        <v>15.6</v>
+      </c>
+      <c r="E440">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B441" t="b">
+        <v>0</v>
+      </c>
+      <c r="C441" t="s">
+        <v>24</v>
+      </c>
+      <c r="D441">
+        <v>12.9</v>
+      </c>
+      <c r="E441">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A442" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B442" t="b">
+        <v>0</v>
+      </c>
+      <c r="C442" t="s">
+        <v>25</v>
+      </c>
+      <c r="D442">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E442">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A443" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B443" t="b">
+        <v>0</v>
+      </c>
+      <c r="C443" t="s">
+        <v>26</v>
+      </c>
+      <c r="D443">
+        <v>11.7</v>
+      </c>
+      <c r="E443">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A444" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B444" t="b">
+        <v>0</v>
+      </c>
+      <c r="C444" t="s">
+        <v>27</v>
+      </c>
+      <c r="D444">
+        <v>13.8</v>
+      </c>
+      <c r="E444">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A445" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B445" t="b">
+        <v>0</v>
+      </c>
+      <c r="C445" t="s">
+        <v>28</v>
+      </c>
+      <c r="D445">
+        <v>16.7</v>
+      </c>
+      <c r="E445">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A446" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B446" t="b">
+        <v>0</v>
+      </c>
+      <c r="C446" t="s">
+        <v>29</v>
+      </c>
+      <c r="D446">
+        <v>11.6</v>
+      </c>
+      <c r="E446">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B447" t="b">
+        <v>0</v>
+      </c>
+      <c r="C447" t="s">
+        <v>30</v>
+      </c>
+      <c r="D447">
+        <v>12.8</v>
+      </c>
+      <c r="E447">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A448" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B448" t="b">
+        <v>0</v>
+      </c>
+      <c r="C448" t="s">
+        <v>31</v>
+      </c>
+      <c r="D448">
+        <v>12.4</v>
+      </c>
+      <c r="E448">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A449" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B449" t="b">
+        <v>0</v>
+      </c>
+      <c r="C449" t="s">
+        <v>32</v>
+      </c>
+      <c r="D449">
+        <v>11.8</v>
+      </c>
+      <c r="E449">
+        <v>12.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A1C21F-8505-41A4-BEA3-B39A3A03BEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79D2D31-1317-4314-A439-0F369EB84247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E449"/>
+  <dimension ref="A1:E477"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -7760,6 +7760,458 @@
         <v>12.3</v>
       </c>
     </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A450" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B450" t="b">
+        <v>1</v>
+      </c>
+      <c r="C450" t="s">
+        <v>5</v>
+      </c>
+      <c r="D450">
+        <v>18</v>
+      </c>
+      <c r="E450">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A451" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B451" t="b">
+        <v>1</v>
+      </c>
+      <c r="C451" t="s">
+        <v>6</v>
+      </c>
+      <c r="D451">
+        <v>14.7</v>
+      </c>
+      <c r="E451">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A452" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B452" t="b">
+        <v>1</v>
+      </c>
+      <c r="C452" t="s">
+        <v>7</v>
+      </c>
+      <c r="D452">
+        <v>14.4</v>
+      </c>
+      <c r="E452">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A453" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B453" t="b">
+        <v>1</v>
+      </c>
+      <c r="C453" t="s">
+        <v>8</v>
+      </c>
+      <c r="D453">
+        <v>14.5</v>
+      </c>
+      <c r="E453">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A454" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B454" t="b">
+        <v>1</v>
+      </c>
+      <c r="C454" t="s">
+        <v>9</v>
+      </c>
+      <c r="D454">
+        <v>13.3</v>
+      </c>
+      <c r="E454">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A455" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B455" t="b">
+        <v>1</v>
+      </c>
+      <c r="C455" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A456" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B456" t="b">
+        <v>1</v>
+      </c>
+      <c r="C456" t="s">
+        <v>11</v>
+      </c>
+      <c r="D456">
+        <v>16.3</v>
+      </c>
+      <c r="E456">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A457" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B457" t="b">
+        <v>1</v>
+      </c>
+      <c r="C457" t="s">
+        <v>12</v>
+      </c>
+      <c r="D457">
+        <v>11.1</v>
+      </c>
+      <c r="E457">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A458" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B458" t="b">
+        <v>1</v>
+      </c>
+      <c r="C458" t="s">
+        <v>13</v>
+      </c>
+      <c r="D458">
+        <v>15.4</v>
+      </c>
+      <c r="E458">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B459" t="b">
+        <v>1</v>
+      </c>
+      <c r="C459" t="s">
+        <v>14</v>
+      </c>
+      <c r="D459">
+        <v>13.8</v>
+      </c>
+      <c r="E459">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B460" t="b">
+        <v>1</v>
+      </c>
+      <c r="C460" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B461" t="b">
+        <v>1</v>
+      </c>
+      <c r="C461" t="s">
+        <v>16</v>
+      </c>
+      <c r="D461">
+        <v>14.5</v>
+      </c>
+      <c r="E461">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B462" t="b">
+        <v>1</v>
+      </c>
+      <c r="C462" t="s">
+        <v>17</v>
+      </c>
+      <c r="D462">
+        <v>14.3</v>
+      </c>
+      <c r="E462">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B463" t="b">
+        <v>1</v>
+      </c>
+      <c r="C463" t="s">
+        <v>18</v>
+      </c>
+      <c r="D463">
+        <v>15.1</v>
+      </c>
+      <c r="E463">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B464" t="b">
+        <v>1</v>
+      </c>
+      <c r="C464" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A465" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B465" t="b">
+        <v>1</v>
+      </c>
+      <c r="C465" t="s">
+        <v>20</v>
+      </c>
+      <c r="D465">
+        <v>12.9</v>
+      </c>
+      <c r="E465">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A466" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B466" t="b">
+        <v>1</v>
+      </c>
+      <c r="C466" t="s">
+        <v>21</v>
+      </c>
+      <c r="D466">
+        <v>15.2</v>
+      </c>
+      <c r="E466">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A467" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B467" t="b">
+        <v>1</v>
+      </c>
+      <c r="C467" t="s">
+        <v>22</v>
+      </c>
+      <c r="D467">
+        <v>11.8</v>
+      </c>
+      <c r="E467">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A468" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B468" t="b">
+        <v>1</v>
+      </c>
+      <c r="C468" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A469" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B469" t="b">
+        <v>1</v>
+      </c>
+      <c r="C469" t="s">
+        <v>24</v>
+      </c>
+      <c r="D469">
+        <v>14.1</v>
+      </c>
+      <c r="E469">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A470" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B470" t="b">
+        <v>1</v>
+      </c>
+      <c r="C470" t="s">
+        <v>25</v>
+      </c>
+      <c r="D470">
+        <v>10</v>
+      </c>
+      <c r="E470">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A471" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B471" t="b">
+        <v>1</v>
+      </c>
+      <c r="C471" t="s">
+        <v>26</v>
+      </c>
+      <c r="D471">
+        <v>14.4</v>
+      </c>
+      <c r="E471">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A472" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B472" t="b">
+        <v>1</v>
+      </c>
+      <c r="C472" t="s">
+        <v>27</v>
+      </c>
+      <c r="D472">
+        <v>15.8</v>
+      </c>
+      <c r="E472">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A473" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B473" t="b">
+        <v>1</v>
+      </c>
+      <c r="C473" t="s">
+        <v>28</v>
+      </c>
+      <c r="D473">
+        <v>16.7</v>
+      </c>
+      <c r="E473">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A474" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B474" t="b">
+        <v>1</v>
+      </c>
+      <c r="C474" t="s">
+        <v>29</v>
+      </c>
+      <c r="D474">
+        <v>14</v>
+      </c>
+      <c r="E474">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A475" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B475" t="b">
+        <v>1</v>
+      </c>
+      <c r="C475" t="s">
+        <v>30</v>
+      </c>
+      <c r="D475">
+        <v>13.9</v>
+      </c>
+      <c r="E475">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A476" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B476" t="b">
+        <v>1</v>
+      </c>
+      <c r="C476" t="s">
+        <v>31</v>
+      </c>
+      <c r="D476">
+        <v>13.4</v>
+      </c>
+      <c r="E476">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A477" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B477" t="b">
+        <v>1</v>
+      </c>
+      <c r="C477" t="s">
+        <v>32</v>
+      </c>
+      <c r="D477">
+        <v>12.6</v>
+      </c>
+      <c r="E477">
+        <v>12.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79D2D31-1317-4314-A439-0F369EB84247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15638C9-9BF6-4A64-9813-5EA266044178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="690" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E477"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -8212,6 +8212,470 @@
         <v>12.7</v>
       </c>
     </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A478" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B478" t="b">
+        <v>0</v>
+      </c>
+      <c r="C478" t="s">
+        <v>5</v>
+      </c>
+      <c r="D478">
+        <v>15</v>
+      </c>
+      <c r="E478">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A479" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B479" t="b">
+        <v>0</v>
+      </c>
+      <c r="C479" t="s">
+        <v>6</v>
+      </c>
+      <c r="D479">
+        <v>13.6</v>
+      </c>
+      <c r="E479">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A480" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B480" t="b">
+        <v>0</v>
+      </c>
+      <c r="C480" t="s">
+        <v>7</v>
+      </c>
+      <c r="D480">
+        <v>15</v>
+      </c>
+      <c r="E480">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A481" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B481" t="b">
+        <v>0</v>
+      </c>
+      <c r="C481" t="s">
+        <v>8</v>
+      </c>
+      <c r="D481">
+        <v>14.2</v>
+      </c>
+      <c r="E481">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A482" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B482" t="b">
+        <v>0</v>
+      </c>
+      <c r="C482" t="s">
+        <v>9</v>
+      </c>
+      <c r="D482">
+        <v>11.9</v>
+      </c>
+      <c r="E482">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A483" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B483" t="b">
+        <v>0</v>
+      </c>
+      <c r="C483" t="s">
+        <v>10</v>
+      </c>
+      <c r="D483">
+        <v>11.8</v>
+      </c>
+      <c r="E483">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A484" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B484" t="b">
+        <v>0</v>
+      </c>
+      <c r="C484" t="s">
+        <v>11</v>
+      </c>
+      <c r="D484">
+        <v>15.2</v>
+      </c>
+      <c r="E484">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A485" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B485" t="b">
+        <v>0</v>
+      </c>
+      <c r="C485" t="s">
+        <v>12</v>
+      </c>
+      <c r="D485">
+        <v>10.3</v>
+      </c>
+      <c r="E485">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A486" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B486" t="b">
+        <v>0</v>
+      </c>
+      <c r="C486" t="s">
+        <v>13</v>
+      </c>
+      <c r="D486">
+        <v>14.2</v>
+      </c>
+      <c r="E486">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A487" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B487" t="b">
+        <v>0</v>
+      </c>
+      <c r="C487" t="s">
+        <v>14</v>
+      </c>
+      <c r="D487">
+        <v>13.6</v>
+      </c>
+      <c r="E487">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A488" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B488" t="b">
+        <v>0</v>
+      </c>
+      <c r="C488" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A489" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B489" t="b">
+        <v>0</v>
+      </c>
+      <c r="C489" t="s">
+        <v>16</v>
+      </c>
+      <c r="D489">
+        <v>14.4</v>
+      </c>
+      <c r="E489">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A490" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B490" t="b">
+        <v>0</v>
+      </c>
+      <c r="C490" t="s">
+        <v>17</v>
+      </c>
+      <c r="D490">
+        <v>12.5</v>
+      </c>
+      <c r="E490">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A491" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B491" t="b">
+        <v>0</v>
+      </c>
+      <c r="C491" t="s">
+        <v>18</v>
+      </c>
+      <c r="D491">
+        <v>13.4</v>
+      </c>
+      <c r="E491">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A492" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B492" t="b">
+        <v>0</v>
+      </c>
+      <c r="C492" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A493" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B493" t="b">
+        <v>0</v>
+      </c>
+      <c r="C493" t="s">
+        <v>20</v>
+      </c>
+      <c r="D493">
+        <v>12.4</v>
+      </c>
+      <c r="E493">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A494" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B494" t="b">
+        <v>0</v>
+      </c>
+      <c r="C494" t="s">
+        <v>21</v>
+      </c>
+      <c r="D494">
+        <v>14.5</v>
+      </c>
+      <c r="E494">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A495" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B495" t="b">
+        <v>0</v>
+      </c>
+      <c r="C495" t="s">
+        <v>22</v>
+      </c>
+      <c r="D495">
+        <v>11.6</v>
+      </c>
+      <c r="E495">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A496" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B496" t="b">
+        <v>0</v>
+      </c>
+      <c r="C496" t="s">
+        <v>23</v>
+      </c>
+      <c r="D496">
+        <v>13.2</v>
+      </c>
+      <c r="E496">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A497" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B497" t="b">
+        <v>0</v>
+      </c>
+      <c r="C497" t="s">
+        <v>24</v>
+      </c>
+      <c r="D497">
+        <v>13.4</v>
+      </c>
+      <c r="E497">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A498" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B498" t="b">
+        <v>0</v>
+      </c>
+      <c r="C498" t="s">
+        <v>25</v>
+      </c>
+      <c r="D498">
+        <v>9.9</v>
+      </c>
+      <c r="E498">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A499" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B499" t="b">
+        <v>0</v>
+      </c>
+      <c r="C499" t="s">
+        <v>26</v>
+      </c>
+      <c r="D499">
+        <v>14</v>
+      </c>
+      <c r="E499">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A500" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B500" t="b">
+        <v>0</v>
+      </c>
+      <c r="C500" t="s">
+        <v>27</v>
+      </c>
+      <c r="D500">
+        <v>13.9</v>
+      </c>
+      <c r="E500">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A501" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B501" t="b">
+        <v>0</v>
+      </c>
+      <c r="C501" t="s">
+        <v>28</v>
+      </c>
+      <c r="D501">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E501">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A502" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B502" t="b">
+        <v>0</v>
+      </c>
+      <c r="C502" t="s">
+        <v>29</v>
+      </c>
+      <c r="D502">
+        <v>12.6</v>
+      </c>
+      <c r="E502">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A503" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B503" t="b">
+        <v>0</v>
+      </c>
+      <c r="C503" t="s">
+        <v>30</v>
+      </c>
+      <c r="D503">
+        <v>12.7</v>
+      </c>
+      <c r="E503">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A504" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B504" t="b">
+        <v>0</v>
+      </c>
+      <c r="C504" t="s">
+        <v>31</v>
+      </c>
+      <c r="D504">
+        <v>14</v>
+      </c>
+      <c r="E504">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A505" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B505" t="b">
+        <v>0</v>
+      </c>
+      <c r="C505" t="s">
+        <v>32</v>
+      </c>
+      <c r="D505">
+        <v>12.8</v>
+      </c>
+      <c r="E505">
+        <v>12.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
